--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.98354</v>
+        <v>16.63403</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71704</v>
+        <v>16.38653</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56656</v>
+        <v>16.39682</v>
       </c>
       <c r="F2" t="n">
-        <v>41.94095</v>
+        <v>42.64991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04933</v>
+        <v>0.05021</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80163</v>
+        <v>1.83523</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.63611</v>
+        <v>16.80694</v>
       </c>
       <c r="D3" t="n">
-        <v>16.35656</v>
+        <v>16.22526</v>
       </c>
       <c r="E3" t="n">
-        <v>16.34788</v>
+        <v>16.54269</v>
       </c>
       <c r="F3" t="n">
-        <v>42.37577</v>
+        <v>42.52254</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05028</v>
+        <v>0.04956</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82998</v>
+        <v>1.84561</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.73009</v>
+        <v>16.76114</v>
       </c>
       <c r="D4" t="n">
-        <v>16.65807</v>
+        <v>16.48346</v>
       </c>
       <c r="E4" t="n">
-        <v>16.50952</v>
+        <v>16.62162</v>
       </c>
       <c r="F4" t="n">
-        <v>42.82162</v>
+        <v>41.50954</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04998</v>
+        <v>0.05079</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81121</v>
+        <v>1.84008</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.53775</v>
+        <v>16.35171</v>
       </c>
       <c r="D6" t="n">
-        <v>16.0826</v>
+        <v>16.01669</v>
       </c>
       <c r="E6" t="n">
-        <v>16.3527</v>
+        <v>16.28036</v>
       </c>
       <c r="F6" t="n">
-        <v>21.63879</v>
+        <v>21.75681</v>
       </c>
       <c r="G6" t="n">
-        <v>34.10679</v>
+        <v>33.32057</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.65991</v>
+        <v>16.91645</v>
       </c>
       <c r="D7" t="n">
-        <v>15.66711</v>
+        <v>15.8385</v>
       </c>
       <c r="E7" t="n">
-        <v>16.449</v>
+        <v>16.55586</v>
       </c>
       <c r="F7" t="n">
-        <v>21.6444</v>
+        <v>21.48798</v>
       </c>
       <c r="G7" t="n">
-        <v>33.6106</v>
+        <v>34.42521</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.29904</v>
+        <v>16.75446</v>
       </c>
       <c r="D8" t="n">
-        <v>15.57367</v>
+        <v>15.32211</v>
       </c>
       <c r="E8" t="n">
-        <v>16.39224</v>
+        <v>16.48858</v>
       </c>
       <c r="F8" t="n">
-        <v>21.51675</v>
+        <v>21.64817</v>
       </c>
       <c r="G8" t="n">
-        <v>33.86621</v>
+        <v>34.5275</v>
       </c>
     </row>
   </sheetData>
